--- a/test_data/Orion_Stress_Demo/PN-BETA-02/40202/BU07/HRM/pre LAM_HRM-2031-0480/Panel 02/Coupon front/2031-03-01_08-00-00_ENG_Orion_Stress_Demo_BU07_Coupon_Front_Summary.xlsx
+++ b/test_data/Orion_Stress_Demo/PN-BETA-02/40202/BU07/HRM/pre LAM_HRM-2031-0480/Panel 02/Coupon front/2031-03-01_08-00-00_ENG_Orion_Stress_Demo_BU07_Coupon_Front_Summary.xlsx
@@ -460,22 +460,22 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>17.70288</v>
+        <v>17.37045</v>
       </c>
       <c r="D2" t="n">
-        <v>17.10422</v>
+        <v>16.81508</v>
       </c>
       <c r="E2" t="n">
-        <v>17.62154</v>
+        <v>17.33978</v>
       </c>
       <c r="F2" t="n">
-        <v>43.74773</v>
+        <v>43.65328</v>
       </c>
       <c r="G2" t="n">
-        <v>0.05194</v>
+        <v>0.0517</v>
       </c>
       <c r="H2" t="n">
-        <v>1.90211</v>
+        <v>1.86795</v>
       </c>
     </row>
     <row r="3">
@@ -485,22 +485,22 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>17.27864</v>
+        <v>17.33032</v>
       </c>
       <c r="D3" t="n">
-        <v>17.08844</v>
+        <v>17.18</v>
       </c>
       <c r="E3" t="n">
-        <v>17.19001</v>
+        <v>17.20104</v>
       </c>
       <c r="F3" t="n">
-        <v>43.63788</v>
+        <v>44.2613</v>
       </c>
       <c r="G3" t="n">
-        <v>0.05188</v>
+        <v>0.05265</v>
       </c>
       <c r="H3" t="n">
-        <v>1.86561</v>
+        <v>1.87549</v>
       </c>
     </row>
     <row r="4">
@@ -510,22 +510,22 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>17.3503</v>
+        <v>17.38614</v>
       </c>
       <c r="D4" t="n">
-        <v>17.23813</v>
+        <v>17.21952</v>
       </c>
       <c r="E4" t="n">
-        <v>17.2243</v>
+        <v>17.29774</v>
       </c>
       <c r="F4" t="n">
-        <v>43.18133</v>
+        <v>43.12562</v>
       </c>
       <c r="G4" t="n">
-        <v>0.05157</v>
+        <v>0.05229</v>
       </c>
       <c r="H4" t="n">
-        <v>1.85951</v>
+        <v>1.8999</v>
       </c>
     </row>
     <row r="5">
@@ -567,19 +567,19 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>17.18754</v>
+        <v>16.81517</v>
       </c>
       <c r="D6" t="n">
-        <v>16.40645</v>
+        <v>16.48069</v>
       </c>
       <c r="E6" t="n">
-        <v>16.89788</v>
+        <v>16.64892</v>
       </c>
       <c r="F6" t="n">
-        <v>22.41779</v>
+        <v>22.62</v>
       </c>
       <c r="G6" t="n">
-        <v>36.07536</v>
+        <v>34.90437</v>
       </c>
     </row>
     <row r="7">
@@ -589,19 +589,19 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>17.20444</v>
+        <v>17.00578</v>
       </c>
       <c r="D7" t="n">
-        <v>16.34366</v>
+        <v>16.65809</v>
       </c>
       <c r="E7" t="n">
-        <v>16.7161</v>
+        <v>16.86693</v>
       </c>
       <c r="F7" t="n">
-        <v>22.39707</v>
+        <v>22.32874</v>
       </c>
       <c r="G7" t="n">
-        <v>34.16932</v>
+        <v>35.66952</v>
       </c>
     </row>
     <row r="8">
@@ -611,19 +611,19 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>17.1666</v>
+        <v>17.29375</v>
       </c>
       <c r="D8" t="n">
-        <v>16.49297</v>
+        <v>16.46042</v>
       </c>
       <c r="E8" t="n">
-        <v>17.13852</v>
+        <v>16.74476</v>
       </c>
       <c r="F8" t="n">
-        <v>22.55825</v>
+        <v>22.87737</v>
       </c>
       <c r="G8" t="n">
-        <v>34.87035</v>
+        <v>35.3572</v>
       </c>
     </row>
     <row r="9">
@@ -650,10 +650,10 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>0.61836</v>
+        <v>0.62953</v>
       </c>
       <c r="D10" t="n">
-        <v>1.13852</v>
+        <v>1.15973</v>
       </c>
     </row>
     <row r="11">
@@ -663,10 +663,10 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>0.63822</v>
+        <v>0.6221</v>
       </c>
       <c r="D11" t="n">
-        <v>1.13994</v>
+        <v>1.12129</v>
       </c>
     </row>
     <row r="12">
@@ -676,10 +676,10 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>0.63389</v>
+        <v>0.63907</v>
       </c>
       <c r="D12" t="n">
-        <v>1.16753</v>
+        <v>1.16562</v>
       </c>
     </row>
   </sheetData>
